--- a/docs/excel-book/projets/Projet1-Budget-personnel.xlsx
+++ b/docs/excel-book/projets/Projet1-Budget-personnel.xlsx
@@ -805,11 +805,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="59870970"/>
-        <c:axId val="78207256"/>
+        <c:axId val="34171584"/>
+        <c:axId val="15151894"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="59870970"/>
+        <c:axId val="34171584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -841,7 +841,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78207256"/>
+        <c:crossAx val="15151894"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -849,7 +849,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="78207256"/>
+        <c:axId val="15151894"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -891,7 +891,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59870970"/>
+        <c:crossAx val="34171584"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1561,7 +1561,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{FF18EA19-118F-4F49-A6AD-8B4BA4D7C7A9}</x14:id>
+          <x14:id>{9E971A50-FD25-42F1-93BA-A07DA06DEB7A}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -1578,7 +1578,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{FF18EA19-118F-4F49-A6AD-8B4BA4D7C7A9}">
+          <x14:cfRule type="dataBar" id="{9E971A50-FD25-42F1-93BA-A07DA06DEB7A}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
